--- a/Data/EXCEL/Transfer/bzPerformance/202210/2404-bzPerformance-202210.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/202210/2404-bzPerformance-202210.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\bzPerformance\202210\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\bzPerformance\202210\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{270BADE2-2395-43DE-AF71-D5AB4836B753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEA0996B-CF90-476D-87B1-D160CA876C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1330" yWindow="3310" windowWidth="15800" windowHeight="8770"/>
+    <workbookView xWindow="570" yWindow="1215" windowWidth="22035" windowHeight="12855"/>
   </bookViews>
   <sheets>
     <sheet name="2404-bzPerformance-202210" sheetId="2" r:id="rId1"/>
@@ -116,7 +116,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -282,7 +282,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="1"/>
+      <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -324,14 +324,6 @@
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="1"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -870,7 +862,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -879,7 +871,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -900,22 +892,22 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1298,21 +1290,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U31"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="6.26953125" customWidth="1"/>
-    <col min="4" max="4" width="6.6328125" customWidth="1"/>
-    <col min="5" max="5" width="6.26953125" customWidth="1"/>
-    <col min="6" max="6" width="6.6328125" customWidth="1"/>
-    <col min="7" max="16" width="6.26953125" customWidth="1"/>
-    <col min="17" max="17" width="6.1796875" customWidth="1"/>
-    <col min="18" max="18" width="6.54296875" customWidth="1"/>
-    <col min="19" max="19" width="6.6328125" customWidth="1"/>
-    <col min="20" max="20" width="6.26953125" customWidth="1"/>
-    <col min="21" max="21" width="7.54296875" customWidth="1"/>
+    <col min="1" max="3" width="7.875" customWidth="1"/>
+    <col min="4" max="4" width="8.25" customWidth="1"/>
+    <col min="5" max="5" width="7.875" customWidth="1"/>
+    <col min="6" max="6" width="8.25" customWidth="1"/>
+    <col min="7" max="17" width="7.875" customWidth="1"/>
+    <col min="18" max="18" width="8.125" customWidth="1"/>
+    <col min="19" max="19" width="8.25" customWidth="1"/>
+    <col min="20" max="20" width="7.875" customWidth="1"/>
+    <col min="21" max="21" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1355,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:21" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -1418,7 +1409,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:21" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="14"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1465,7 +1456,7 @@
       </c>
       <c r="U3" s="3"/>
     </row>
-    <row r="4" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>27</v>
       </c>
@@ -1530,7 +1521,7 @@
         <v>42.93</v>
       </c>
     </row>
-    <row r="5" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="19"/>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
@@ -1557,7 +1548,7 @@
       <c r="T5" s="25"/>
       <c r="U5" s="21"/>
     </row>
-    <row r="6" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>2021</v>
       </c>
@@ -1622,7 +1613,7 @@
         <v>50.41</v>
       </c>
     </row>
-    <row r="7" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>2020</v>
       </c>
@@ -1687,7 +1678,7 @@
         <v>52.49</v>
       </c>
     </row>
-    <row r="8" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>2019</v>
       </c>
@@ -1752,7 +1743,7 @@
         <v>44.95</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>2018</v>
       </c>
@@ -1817,7 +1808,7 @@
         <v>38.06</v>
       </c>
     </row>
-    <row r="10" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>2017</v>
       </c>
@@ -1882,7 +1873,7 @@
         <v>26.87</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>2016</v>
       </c>
@@ -1947,7 +1938,7 @@
         <v>27.79</v>
       </c>
     </row>
-    <row r="12" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>2015</v>
       </c>
@@ -2012,7 +2003,7 @@
         <v>26.05</v>
       </c>
     </row>
-    <row r="13" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>2014</v>
       </c>
@@ -2077,7 +2068,7 @@
         <v>23.33</v>
       </c>
     </row>
-    <row r="14" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>2013</v>
       </c>
@@ -2142,7 +2133,7 @@
         <v>22.33</v>
       </c>
     </row>
-    <row r="15" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>2012</v>
       </c>
@@ -2207,7 +2198,7 @@
         <v>19.64</v>
       </c>
     </row>
-    <row r="16" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>2011</v>
       </c>
@@ -2272,7 +2263,7 @@
         <v>20.63</v>
       </c>
     </row>
-    <row r="17" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>2010</v>
       </c>
@@ -2337,7 +2328,7 @@
         <v>21.27</v>
       </c>
     </row>
-    <row r="18" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>2009</v>
       </c>
@@ -2402,7 +2393,7 @@
         <v>16.95</v>
       </c>
     </row>
-    <row r="19" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>2008</v>
       </c>
@@ -2467,7 +2458,7 @@
         <v>16.39</v>
       </c>
     </row>
-    <row r="20" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>2007</v>
       </c>
@@ -2532,7 +2523,7 @@
         <v>18.55</v>
       </c>
     </row>
-    <row r="21" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>2006</v>
       </c>
@@ -2597,7 +2588,7 @@
         <v>17.36</v>
       </c>
     </row>
-    <row r="22" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>2005</v>
       </c>
@@ -2662,7 +2653,7 @@
         <v>17.71</v>
       </c>
     </row>
-    <row r="23" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>2004</v>
       </c>
@@ -2727,7 +2718,7 @@
         <v>18.13</v>
       </c>
     </row>
-    <row r="24" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>2003</v>
       </c>
@@ -2792,7 +2783,7 @@
         <v>16.559999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>2002</v>
       </c>
@@ -2857,7 +2848,7 @@
         <v>14.61</v>
       </c>
     </row>
-    <row r="26" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>2001</v>
       </c>
@@ -2922,7 +2913,7 @@
         <v>13.91</v>
       </c>
     </row>
-    <row r="27" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>2000</v>
       </c>
@@ -2987,7 +2978,7 @@
         <v>16.670000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>1999</v>
       </c>
@@ -3052,7 +3043,7 @@
         <v>19.03</v>
       </c>
     </row>
-    <row r="29" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>1998</v>
       </c>
@@ -3117,7 +3108,7 @@
         <v>20.69</v>
       </c>
     </row>
-    <row r="30" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>1997</v>
       </c>
@@ -3182,7 +3173,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:21" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>1996</v>
       </c>
@@ -3277,7 +3268,7 @@
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
   </mergeCells>
-  <phoneticPr fontId="26" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>